--- a/desktop/tests/fixtures/doc-comments/q3-sales-by-rep.xlsx
+++ b/desktop/tests/fixtures/doc-comments/q3-sales-by-rep.xlsx
@@ -24,6 +24,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <t>Priya Shah: Reserved for the September actuals once they post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
+          <t>Diego mentioned this figure needs a second look before the board meeting.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <t>Check this number: 42 seems low for August.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -46,7 +67,23 @@
         <r>
           <t xml:space="preserve">Priya Shah: Diego’s numbers look great this quarter.
 Marcus Lee: Agreed — his new accounts are paying off.
+​✓ Resolved</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Priya Shah: Did the refunds line get double-counted?
+Marcus Lee: Checked — it did not, the total already excludes them.
 ​[[yc:resolved]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0">
+      <text>
+        <r>
+          <t>Marcus Lee: Following up next week. ✓ Resolved</t>
         </r>
       </text>
     </comment>
@@ -55,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="19">
   <si>
     <t>Region</t>
   </si>
@@ -106,6 +143,9 @@
   </si>
   <si>
     <t>Sep</t>
+  </si>
+  <si>
+    <t>flagged</t>
   </si>
   <si>
     <t>Q3 total</t>
@@ -135,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -143,13 +183,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -721,6 +769,19 @@
         <v>16</v>
       </c>
     </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -730,7 +791,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -741,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -782,6 +843,11 @@
       </c>
       <c r="B6">
         <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
